--- a/public/samples/pt-BR/sample-group.xlsx
+++ b/public/samples/pt-BR/sample-group.xlsx
@@ -35,7 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,10 +79,11 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +502,7 @@
       <c r="C3" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>7.1</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -519,7 +522,7 @@
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>6.6</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -539,7 +542,7 @@
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>6.7</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -559,7 +562,7 @@
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>6.5</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -579,7 +582,7 @@
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>7.1</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -599,7 +602,7 @@
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>8.1</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -619,7 +622,7 @@
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>8.1</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -639,7 +642,7 @@
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>7.9</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -659,7 +662,7 @@
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>7.4</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -679,7 +682,7 @@
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>8.4</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -699,7 +702,7 @@
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>5.9</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -719,7 +722,7 @@
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>7.4</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -739,8 +742,8 @@
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D15" s="2" t="str">
-        <v>7.0</v>
+      <c r="D15" s="3">
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="str">
         <v/>
@@ -759,7 +762,7 @@
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>8.2</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -779,7 +782,7 @@
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>6.8</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -799,7 +802,7 @@
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>6.5</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -819,7 +822,7 @@
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>6.1</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -839,8 +842,8 @@
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D20" s="2" t="str">
-        <v>7.0</v>
+      <c r="D20" s="3">
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="str">
         <v/>
@@ -859,7 +862,7 @@
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>7.8</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -879,7 +882,7 @@
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>7.2</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -899,8 +902,8 @@
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D23" s="2" t="str">
-        <v>7.0</v>
+      <c r="D23" s="3">
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="str">
         <v/>
@@ -919,7 +922,7 @@
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>7.2</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -939,7 +942,7 @@
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>7.6</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -959,7 +962,7 @@
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>7.9</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -979,7 +982,7 @@
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>7.8</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -999,7 +1002,7 @@
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>7.2</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1019,7 +1022,7 @@
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>6.5</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1039,8 +1042,8 @@
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D30" s="2" t="str">
-        <v>8.0</v>
+      <c r="D30" s="3">
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="str">
         <v/>
@@ -1059,7 +1062,7 @@
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>8.5</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -1079,7 +1082,7 @@
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>7.1</v>
       </c>
       <c r="E32" s="2" t="str">

--- a/public/samples/pt-BR/sample-group.xlsx
+++ b/public/samples/pt-BR/sample-group.xlsx
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +471,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +489,12 @@
         <v>Média</v>
       </c>
       <c r="E2" s="2" t="str">
+        <v>Nível de leitura</v>
+      </c>
+      <c r="F2" s="2" t="str">
         <v>Liderança</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="G2" s="2" t="str">
         <v>Grupo anterior</v>
       </c>
     </row>
@@ -497,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Helena Barbosa</v>
+        <v>Helena Rodrigues</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +511,14 @@
       <c r="D3" s="3">
         <v>7.1</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="2">
-        <v>2</v>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -517,19 +526,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Miguel Almeida</v>
+        <v>Miguel Santos</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="2">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -537,19 +549,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Alice Martins</v>
+        <v>Alice Ribeiro</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
+        <v>7.8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +572,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Arthur Ribeiro</v>
+        <v>Arthur Rodrigues</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +595,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Laura Lima</v>
+        <v>Laura Carvalho</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="2">
         <v>4</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -597,18 +618,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Gael Silva</v>
+        <v>Gael Santos</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F8" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2">
         <v>5</v>
       </c>
     </row>
@@ -617,19 +641,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Maria Alice Santos</v>
+        <v>Maria Alice Carvalho</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="2">
-        <v>5</v>
+        <v>7.9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -637,19 +664,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Heitor Ferreira</v>
+        <v>Heitor Alves</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
+        <v>7.7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +687,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Valentina Lopes</v>
+        <v>Valentina Oliveira</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F11" s="2">
-        <v>3</v>
+        <v>8.1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -683,13 +716,16 @@
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>8.4</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="2">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +733,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Heloísa Soares</v>
+        <v>Heloísa Carvalho</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F13" s="2">
-        <v>6</v>
+        <v>7.7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -717,19 +756,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Davi Almeida</v>
+        <v>Davi Carvalho</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F14" s="2">
-        <v>5</v>
+        <v>8.4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -737,19 +779,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Maria Clara Soares</v>
+        <v>Maria Clara Souza</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <v>5</v>
+        <v>6.8</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -757,19 +802,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Gabriel Carvalho</v>
+        <v>Gabriel Oliveira</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E16" s="2" t="str">
+        <v>6.4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
+      <c r="G16" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -777,19 +825,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Cecília Ribeiro</v>
+        <v>Cecília Silva</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F17" s="2">
-        <v>6</v>
+        <v>7.3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +848,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Bernardo Silva</v>
+        <v>Bernardo Ferreira</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F18" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2">
         <v>5</v>
       </c>
     </row>
@@ -823,13 +877,16 @@
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
+        <v>6.6</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -837,19 +894,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Samuel Costa</v>
+        <v>Samuel Carvalho</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F20" s="2">
-        <v>4</v>
+        <v>7.7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -857,19 +917,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Sophia Costa</v>
+        <v>Sophia Vieira</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
+        <v>7.2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -877,19 +940,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>João Miguel Barbosa</v>
+        <v>João Miguel Fernandes</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F22" s="2">
-        <v>3</v>
+        <v>6.8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +963,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Manuela Carvalho</v>
+        <v>Manuela Soares</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="3">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F23" s="2">
         <v>6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -917,19 +986,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Pedro Carvalho</v>
+        <v>Pedro Souza</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <v>3</v>
+        <v>6.5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -937,19 +1009,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Isabela Ribeiro</v>
+        <v>Isabela Barbosa</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="2">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -957,7 +1032,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Costa</v>
+        <v>Lucas Vieira</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
@@ -965,11 +1040,14 @@
       <c r="D26" s="3">
         <v>7.9</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="E26" s="2">
         <v>2</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -977,19 +1055,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Lívia Rodrigues</v>
+        <v>Lívia Soares</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F27" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E27" s="2">
         <v>2</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -997,19 +1078,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Rafael Barbosa</v>
+        <v>Rafael Lopes</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1</v>
+        <v>6.2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1101,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Beatriz Santos</v>
+        <v>Beatriz Alves</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="2">
-        <v>6</v>
+        <v>6.2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G29" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1037,19 +1124,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Enzo Vieira</v>
+        <v>Enzo Pereira</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="3">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="2">
-        <v>5</v>
+        <v>8.1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1057,19 +1147,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Luiza Pereira</v>
+        <v>Luiza Ferreira</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="2">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="E31" s="2">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1077,24 +1170,27 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Matheus Fernandes</v>
+        <v>Matheus Barbosa</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1115,37 +1211,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/pt-BR/sample-group.xlsx
+++ b/public/samples/pt-BR/sample-group.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de alunos" sheetId="2" r:id="rId2"/>
     <sheet name="Manter juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Critérios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -1249,4 +1250,90 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Critério</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opções</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gênero</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Média</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nível de leitura</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nível</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Liderança</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Caixa de seleção</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Grupo anterior</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/pt-BR/sample-group.xlsx
+++ b/public/samples/pt-BR/sample-group.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de alunos" sheetId="2" r:id="rId2"/>
     <sheet name="Manter juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Critérios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -450,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +472,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +490,12 @@
         <v>Média</v>
       </c>
       <c r="E2" s="2" t="str">
+        <v>Nível de leitura</v>
+      </c>
+      <c r="F2" s="2" t="str">
         <v>Liderança</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="G2" s="2" t="str">
         <v>Grupo anterior</v>
       </c>
     </row>
@@ -497,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Helena Barbosa</v>
+        <v>Helena Rodrigues</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +512,14 @@
       <c r="D3" s="3">
         <v>7.1</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="2">
-        <v>2</v>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -517,19 +527,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Miguel Almeida</v>
+        <v>Miguel Santos</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="2">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -537,19 +550,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Alice Martins</v>
+        <v>Alice Ribeiro</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
+        <v>7.8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +573,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Arthur Ribeiro</v>
+        <v>Arthur Rodrigues</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +596,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Laura Lima</v>
+        <v>Laura Carvalho</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="2">
         <v>4</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -597,18 +619,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Gael Silva</v>
+        <v>Gael Santos</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F8" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="2">
         <v>5</v>
       </c>
     </row>
@@ -617,19 +642,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Maria Alice Santos</v>
+        <v>Maria Alice Carvalho</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="2">
-        <v>5</v>
+        <v>7.9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -637,19 +665,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Heitor Ferreira</v>
+        <v>Heitor Alves</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
+        <v>7.7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +688,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Valentina Lopes</v>
+        <v>Valentina Oliveira</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F11" s="2">
-        <v>3</v>
+        <v>8.1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -683,13 +717,16 @@
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>8.4</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="2">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +734,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Heloísa Soares</v>
+        <v>Heloísa Carvalho</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F13" s="2">
-        <v>6</v>
+        <v>7.7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -717,19 +757,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Davi Almeida</v>
+        <v>Davi Carvalho</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>7.4</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F14" s="2">
-        <v>5</v>
+        <v>8.4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -737,19 +780,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Maria Clara Soares</v>
+        <v>Maria Clara Souza</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <v>5</v>
+        <v>6.8</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -757,19 +803,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Gabriel Carvalho</v>
+        <v>Gabriel Oliveira</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="E16" s="2" t="str">
+        <v>6.4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
+      <c r="G16" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -777,19 +826,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Cecília Ribeiro</v>
+        <v>Cecília Silva</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F17" s="2">
-        <v>6</v>
+        <v>7.3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +849,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Bernardo Silva</v>
+        <v>Bernardo Ferreira</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F18" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2">
         <v>5</v>
       </c>
     </row>
@@ -823,13 +878,16 @@
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
+        <v>6.6</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -837,19 +895,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Samuel Costa</v>
+        <v>Samuel Carvalho</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F20" s="2">
-        <v>4</v>
+        <v>7.7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -857,19 +918,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Sophia Costa</v>
+        <v>Sophia Vieira</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
+        <v>7.2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -877,19 +941,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>João Miguel Barbosa</v>
+        <v>João Miguel Fernandes</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F22" s="2">
-        <v>3</v>
+        <v>6.8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -897,19 +964,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Manuela Carvalho</v>
+        <v>Manuela Soares</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="3">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F23" s="2">
         <v>6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -917,19 +987,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Pedro Carvalho</v>
+        <v>Pedro Souza</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <v>3</v>
+        <v>6.5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -937,19 +1010,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Isabela Ribeiro</v>
+        <v>Isabela Barbosa</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>7.6</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="2">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -957,7 +1033,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Costa</v>
+        <v>Lucas Vieira</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
@@ -965,11 +1041,14 @@
       <c r="D26" s="3">
         <v>7.9</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="E26" s="2">
         <v>2</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -977,19 +1056,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Lívia Rodrigues</v>
+        <v>Lívia Soares</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="3">
-        <v>7.8</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F27" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E27" s="2">
         <v>2</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -997,19 +1079,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Rafael Barbosa</v>
+        <v>Rafael Lopes</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v>✓</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1</v>
+        <v>6.2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1102,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Beatriz Santos</v>
+        <v>Beatriz Alves</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="2">
-        <v>6</v>
+        <v>6.2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G29" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1037,19 +1125,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Enzo Vieira</v>
+        <v>Enzo Pereira</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="3">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="2">
-        <v>5</v>
+        <v>8.1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1057,19 +1148,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Luiza Pereira</v>
+        <v>Luiza Ferreira</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="2">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="E31" s="2">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1077,24 +1171,27 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Matheus Fernandes</v>
+        <v>Matheus Barbosa</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1115,37 +1212,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1153,4 +1250,90 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Critério</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opções</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gênero</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Média</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nível de leitura</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nível</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Liderança</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Caixa de seleção</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Grupo anterior</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+  </ignoredErrors>
+</worksheet>
 </file>